--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92573535264</v>
+        <v>46157.93114551402</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114551402</v>
+        <v>46157.93181194014</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93181194014</v>
+        <v>46157.93404921978</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93404921978</v>
+        <v>46157.9372299907</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372299907</v>
+        <v>46158.28220851308</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28220851308</v>
+        <v>46158.29698029502</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29698029502</v>
+        <v>46158.29820467053</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820467053</v>
+        <v>46158.33391834892</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33391834892</v>
+        <v>46158.36861640036</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Грачев - соц работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861640036</v>
+        <v>46158.37292271565</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
